--- a/data/base/Backlog_35.xlsx
+++ b/data/base/Backlog_35.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C987AF-A3A4-4435-9AE4-3A1411F3FBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A26FB3-E75F-46CC-9A3A-0ECBBA166F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{95CF10DA-EF2D-4A9B-952E-EAB842DF9BF3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{95CF10DA-EF2D-4A9B-952E-EAB842DF9BF3}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
     <sheet name="SPN" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -263,7 +264,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,18 +442,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -633,31 +622,31 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="21" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1036,54 +1025,55 @@
   <dimension ref="A1:AT27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="23" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="28" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="31" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="59.28515625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="40.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="34.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="33.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="28" style="2" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="31" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="59.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
@@ -1121,1048 +1111,1049 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="4">
-        <v>35</v>
-      </c>
-      <c r="E2" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="C2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="3">
+        <v>35</v>
+      </c>
+      <c r="E2" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G2" s="3">
         <v>23459</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>46235</v>
       </c>
-      <c r="I2" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="I2" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="9"/>
-      <c r="M2" s="10"/>
+      <c r="M2" s="8"/>
       <c r="O2" s="9"/>
-      <c r="AS2" s="10"/>
+      <c r="AS2" s="8"/>
       <c r="AT2" s="9"/>
     </row>
-    <row r="3" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="4">
-        <v>35</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="C3" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="3">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G3" s="3">
         <v>23491</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>46235</v>
       </c>
-      <c r="I3" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="I3" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="9"/>
-      <c r="M3" s="10"/>
+      <c r="M3" s="8"/>
       <c r="O3" s="9"/>
-      <c r="AS3" s="10"/>
+      <c r="AS3" s="8"/>
       <c r="AT3" s="9"/>
     </row>
-    <row r="4" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="4">
-        <v>35</v>
-      </c>
-      <c r="E4" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="C4" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="3">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F4" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G4" s="3">
         <v>23747</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>46235</v>
       </c>
-      <c r="I4" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="I4" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
+      <c r="M4" s="8"/>
       <c r="O4" s="9"/>
-      <c r="AS4" s="10"/>
+      <c r="AS4" s="8"/>
       <c r="AT4" s="9"/>
     </row>
-    <row r="5" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="4">
-        <v>35</v>
-      </c>
-      <c r="E5" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="C5" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="3">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G5" s="3">
         <v>23825</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>46235</v>
       </c>
-      <c r="I5" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="I5" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
+      <c r="M5" s="8"/>
       <c r="O5" s="9"/>
-      <c r="AS5" s="10"/>
+      <c r="AS5" s="8"/>
       <c r="AT5" s="9"/>
     </row>
-    <row r="6" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="4">
-        <v>35</v>
-      </c>
-      <c r="E6" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="C6" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="3">
+        <v>35</v>
+      </c>
+      <c r="E6" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F6" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G6" s="3">
         <v>23942</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>46235</v>
       </c>
-      <c r="I6" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="8" t="s">
+      <c r="I6" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="9"/>
-      <c r="M6" s="10"/>
+      <c r="M6" s="8"/>
       <c r="O6" s="9"/>
-      <c r="AS6" s="10"/>
+      <c r="AS6" s="8"/>
       <c r="AT6" s="9"/>
     </row>
-    <row r="7" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="4">
-        <v>35</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="C7" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="3">
+        <v>35</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F7" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G7" s="3">
         <v>24002</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>46235</v>
       </c>
-      <c r="I7" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="I7" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="9"/>
-      <c r="M7" s="10"/>
+      <c r="M7" s="8"/>
       <c r="O7" s="9"/>
-      <c r="AS7" s="10"/>
+      <c r="AS7" s="8"/>
       <c r="AT7" s="9"/>
     </row>
-    <row r="8" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="4">
-        <v>35</v>
-      </c>
-      <c r="E8" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="C8" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="3">
+        <v>35</v>
+      </c>
+      <c r="E8" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F8" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G8" s="3">
         <v>24087</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>46235</v>
       </c>
-      <c r="I8" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="9"/>
-      <c r="M8" s="10"/>
+      <c r="M8" s="8"/>
       <c r="O8" s="9"/>
-      <c r="AS8" s="10"/>
+      <c r="AS8" s="8"/>
       <c r="AT8" s="9"/>
     </row>
-    <row r="9" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="4">
-        <v>35</v>
-      </c>
-      <c r="E9" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="C9" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="3">
+        <v>35</v>
+      </c>
+      <c r="E9" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F9" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G9" s="3">
         <v>24100</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>46235</v>
       </c>
-      <c r="I9" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="I9" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="9"/>
-      <c r="M9" s="10"/>
-      <c r="AS9" s="10"/>
+      <c r="M9" s="8"/>
+      <c r="AS9" s="8"/>
       <c r="AT9" s="9"/>
     </row>
-    <row r="10" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="4">
-        <v>35</v>
-      </c>
-      <c r="E10" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="C10" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="3">
+        <v>35</v>
+      </c>
+      <c r="E10" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F10" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G10" s="3">
         <v>24204</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>46266</v>
       </c>
-      <c r="I10" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="I10" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="9"/>
-      <c r="M10" s="10"/>
+      <c r="M10" s="8"/>
       <c r="O10" s="9"/>
-      <c r="AS10" s="10"/>
+      <c r="AS10" s="8"/>
       <c r="AT10" s="9"/>
     </row>
-    <row r="11" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="4">
-        <v>35</v>
-      </c>
-      <c r="E11" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="C11" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="3">
+        <v>35</v>
+      </c>
+      <c r="E11" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F11" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G11" s="3">
         <v>24215</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>46266</v>
       </c>
-      <c r="I11" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="I11" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="9"/>
-      <c r="M11" s="10"/>
+      <c r="M11" s="8"/>
       <c r="O11" s="9"/>
-      <c r="AS11" s="10"/>
+      <c r="AS11" s="8"/>
       <c r="AT11" s="9"/>
     </row>
-    <row r="12" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="4">
-        <v>35</v>
-      </c>
-      <c r="E12" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="C12" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="3">
+        <v>35</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F12" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G12" s="3">
         <v>24222</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>46266</v>
       </c>
-      <c r="I12" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="8" t="s">
+      <c r="I12" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="9"/>
-      <c r="M12" s="10"/>
+      <c r="M12" s="8"/>
       <c r="O12" s="9"/>
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
-      <c r="AS12" s="10"/>
+      <c r="AS12" s="8"/>
       <c r="AT12" s="9"/>
     </row>
-    <row r="13" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="4">
-        <v>35</v>
-      </c>
-      <c r="E13" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F13" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="C13" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="3">
+        <v>35</v>
+      </c>
+      <c r="E13" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F13" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G13" s="3">
         <v>24224</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>46266</v>
       </c>
-      <c r="I13" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="8" t="s">
+      <c r="I13" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L13" s="9"/>
-      <c r="M13" s="10"/>
+      <c r="M13" s="8"/>
       <c r="O13" s="9"/>
-      <c r="AS13" s="10"/>
+      <c r="AS13" s="8"/>
       <c r="AT13" s="9"/>
     </row>
-    <row r="14" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="4">
-        <v>35</v>
-      </c>
-      <c r="E14" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="C14" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="3">
+        <v>35</v>
+      </c>
+      <c r="E14" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F14" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G14" s="3">
         <v>24226</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>46266</v>
       </c>
-      <c r="I14" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="8" t="s">
+      <c r="I14" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L14" s="9"/>
-      <c r="M14" s="10"/>
-      <c r="AS14" s="10"/>
+      <c r="M14" s="8"/>
+      <c r="AS14" s="8"/>
       <c r="AT14" s="9"/>
     </row>
-    <row r="15" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="4">
-        <v>35</v>
-      </c>
-      <c r="E15" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="C15" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="3">
+        <v>35</v>
+      </c>
+      <c r="E15" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F15" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G15" s="3">
         <v>24231</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>46266</v>
       </c>
-      <c r="I15" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="I15" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="9"/>
-      <c r="M15" s="10"/>
-      <c r="AS15" s="10"/>
+      <c r="M15" s="8"/>
+      <c r="AS15" s="8"/>
       <c r="AT15" s="9"/>
     </row>
-    <row r="16" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="4">
-        <v>35</v>
-      </c>
-      <c r="E16" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F16" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G16" s="4">
+      <c r="C16" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="3">
+        <v>35</v>
+      </c>
+      <c r="E16" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F16" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G16" s="3">
         <v>24245</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="6">
         <v>46266</v>
       </c>
-      <c r="I16" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="8" t="s">
+      <c r="I16" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="9"/>
-      <c r="M16" s="10"/>
+      <c r="M16" s="8"/>
       <c r="O16" s="9"/>
-      <c r="AS16" s="10"/>
+      <c r="AS16" s="8"/>
       <c r="AT16" s="9"/>
     </row>
-    <row r="17" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="4">
-        <v>35</v>
-      </c>
-      <c r="E17" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="C17" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="3">
+        <v>35</v>
+      </c>
+      <c r="E17" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F17" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G17" s="3">
         <v>24248</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>46266</v>
       </c>
-      <c r="I17" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="8" t="s">
+      <c r="I17" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L17" s="9"/>
-      <c r="M17" s="10"/>
+      <c r="M17" s="8"/>
       <c r="O17" s="9"/>
-      <c r="AS17" s="10"/>
+      <c r="AS17" s="8"/>
       <c r="AT17" s="9"/>
     </row>
-    <row r="18" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="4">
-        <v>35</v>
-      </c>
-      <c r="E18" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G18" s="4">
+      <c r="C18" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="3">
+        <v>35</v>
+      </c>
+      <c r="E18" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F18" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G18" s="3">
         <v>24287</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>46266</v>
       </c>
-      <c r="I18" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="8" t="s">
+      <c r="I18" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L18" s="9"/>
-      <c r="M18" s="10"/>
+      <c r="M18" s="8"/>
       <c r="O18" s="9"/>
-      <c r="AS18" s="10"/>
+      <c r="AS18" s="8"/>
       <c r="AT18" s="9"/>
     </row>
-    <row r="19" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="4">
-        <v>35</v>
-      </c>
-      <c r="E19" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="C19" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="3">
+        <v>35</v>
+      </c>
+      <c r="E19" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F19" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G19" s="3">
         <v>24342</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>46266</v>
       </c>
-      <c r="I19" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="8" t="s">
+      <c r="I19" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L19" s="9"/>
-      <c r="M19" s="10"/>
+      <c r="M19" s="8"/>
       <c r="O19" s="9"/>
-      <c r="AS19" s="10"/>
+      <c r="AS19" s="8"/>
       <c r="AT19" s="9"/>
     </row>
-    <row r="20" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="4">
-        <v>35</v>
-      </c>
-      <c r="E20" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="C20" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="3">
+        <v>35</v>
+      </c>
+      <c r="E20" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F20" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G20" s="3">
         <v>24343</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>46266</v>
       </c>
-      <c r="I20" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="8" t="s">
+      <c r="I20" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L20" s="9"/>
-      <c r="M20" s="10"/>
+      <c r="M20" s="8"/>
       <c r="O20" s="9"/>
-      <c r="AS20" s="10"/>
+      <c r="AS20" s="8"/>
       <c r="AT20" s="9"/>
     </row>
-    <row r="21" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="4">
-        <v>35</v>
-      </c>
-      <c r="E21" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="C21" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="3">
+        <v>35</v>
+      </c>
+      <c r="E21" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F21" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G21" s="3">
         <v>24344</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="6">
         <v>46266</v>
       </c>
-      <c r="I21" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="8" t="s">
+      <c r="I21" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L21" s="9"/>
-      <c r="M21" s="10"/>
+      <c r="M21" s="8"/>
       <c r="O21" s="9"/>
-      <c r="AS21" s="10"/>
+      <c r="AS21" s="8"/>
       <c r="AT21" s="9"/>
     </row>
-    <row r="22" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="4">
-        <v>35</v>
-      </c>
-      <c r="E22" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F22" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="C22" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="3">
+        <v>35</v>
+      </c>
+      <c r="E22" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F22" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G22" s="3">
         <v>24366</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="6">
         <v>46266</v>
       </c>
-      <c r="I22" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="8" t="s">
+      <c r="I22" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="9"/>
-      <c r="M22" s="10"/>
+      <c r="M22" s="8"/>
       <c r="O22" s="9"/>
-      <c r="AS22" s="10"/>
+      <c r="AS22" s="8"/>
       <c r="AT22" s="9"/>
     </row>
-    <row r="23" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="4">
-        <v>35</v>
-      </c>
-      <c r="E23" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="C23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="3">
+        <v>35</v>
+      </c>
+      <c r="E23" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F23" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G23" s="3">
         <v>24404</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="6">
         <v>46266</v>
       </c>
-      <c r="I23" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="I23" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L23" s="9"/>
-      <c r="M23" s="10"/>
+      <c r="M23" s="8"/>
       <c r="O23" s="9"/>
-      <c r="AS23" s="10"/>
+      <c r="AS23" s="8"/>
       <c r="AT23" s="9"/>
     </row>
-    <row r="24" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="4">
-        <v>35</v>
-      </c>
-      <c r="E24" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="C24" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="3">
+        <v>35</v>
+      </c>
+      <c r="E24" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F24" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G24" s="3">
         <v>24416</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="6">
         <v>46266</v>
       </c>
-      <c r="I24" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="I24" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="K24" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L24" s="9"/>
-      <c r="M24" s="10"/>
+      <c r="M24" s="8"/>
       <c r="O24" s="9"/>
-      <c r="AS24" s="10"/>
+      <c r="AS24" s="8"/>
       <c r="AT24" s="9"/>
     </row>
-    <row r="25" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="4">
-        <v>35</v>
-      </c>
-      <c r="E25" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F25" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="C25" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="3">
+        <v>35</v>
+      </c>
+      <c r="E25" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F25" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G25" s="3">
         <v>24424</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="6">
         <v>46266</v>
       </c>
-      <c r="I25" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="8" t="s">
+      <c r="I25" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="9"/>
-      <c r="M25" s="10"/>
+      <c r="M25" s="8"/>
       <c r="O25" s="9"/>
-      <c r="AS25" s="10"/>
+      <c r="AS25" s="8"/>
       <c r="AT25" s="9"/>
     </row>
-    <row r="26" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="4">
-        <v>35</v>
-      </c>
-      <c r="E26" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F26" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="C26" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="3">
+        <v>35</v>
+      </c>
+      <c r="E26" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F26" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G26" s="3">
         <v>24444</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>46266</v>
       </c>
-      <c r="I26" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J26" s="5" t="s">
+      <c r="I26" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="K26" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L26" s="9"/>
-      <c r="M26" s="10"/>
+      <c r="M26" s="8"/>
       <c r="O26" s="9"/>
-      <c r="AS26" s="10"/>
+      <c r="AS26" s="8"/>
       <c r="AT26" s="9"/>
     </row>
-    <row r="27" spans="1:46" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="4">
-        <v>35</v>
-      </c>
-      <c r="E27" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F27" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="C27" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="3">
+        <v>35</v>
+      </c>
+      <c r="E27" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F27" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G27" s="3">
         <v>24451</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>46266</v>
       </c>
-      <c r="I27" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K27" s="8" t="s">
+      <c r="I27" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L27" s="9"/>
-      <c r="M27" s="10"/>
+      <c r="M27" s="8"/>
       <c r="O27" s="9"/>
       <c r="Y27" s="9"/>
       <c r="Z27" s="9"/>
-      <c r="AS27" s="10"/>
+      <c r="AS27" s="8"/>
       <c r="AT27" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{349D8DFF-FFE7-45CA-B67A-40C93DB9EFC7}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -2172,42 +2163,43 @@
   <dimension ref="A1:AI18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="33.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="59.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
@@ -2245,537 +2237,537 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="4">
-        <v>35</v>
-      </c>
-      <c r="E2" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="C2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="3">
+        <v>35</v>
+      </c>
+      <c r="E2" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G2" s="3">
         <v>24123</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>46235</v>
       </c>
-      <c r="I2" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH2" s="10"/>
+      <c r="AH2" s="8"/>
       <c r="AI2" s="9"/>
     </row>
-    <row r="3" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="4">
-        <v>35</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="C3" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="3">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G3" s="3">
         <v>24062</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>46235</v>
       </c>
-      <c r="I3" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="I3" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH3" s="10"/>
+      <c r="AH3" s="8"/>
       <c r="AI3" s="9"/>
     </row>
-    <row r="4" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="4">
-        <v>35</v>
-      </c>
-      <c r="E4" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="C4" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="3">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F4" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G4" s="3">
         <v>24182</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>46266</v>
       </c>
-      <c r="I4" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH4" s="10"/>
+      <c r="AH4" s="8"/>
       <c r="AI4" s="9"/>
     </row>
-    <row r="5" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="4">
-        <v>35</v>
-      </c>
-      <c r="E5" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="C5" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="3">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G5" s="3">
         <v>24284</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>46266</v>
       </c>
-      <c r="I5" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="I5" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH5" s="10"/>
+      <c r="AH5" s="8"/>
       <c r="AI5" s="9"/>
     </row>
-    <row r="6" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="4">
-        <v>35</v>
-      </c>
-      <c r="E6" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="C6" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="3">
+        <v>35</v>
+      </c>
+      <c r="E6" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F6" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G6" s="3">
         <v>22908</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>46235</v>
       </c>
-      <c r="I6" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="I6" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>26</v>
       </c>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
-      <c r="AH6" s="10"/>
+      <c r="AH6" s="8"/>
       <c r="AI6" s="9"/>
     </row>
-    <row r="7" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="4">
-        <v>35</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="C7" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="3">
+        <v>35</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F7" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G7" s="3">
         <v>23490</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>46235</v>
       </c>
-      <c r="I7" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="I7" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH7" s="10"/>
+      <c r="AH7" s="8"/>
       <c r="AI7" s="9"/>
     </row>
-    <row r="8" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="4">
-        <v>35</v>
-      </c>
-      <c r="E8" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="C8" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="3">
+        <v>35</v>
+      </c>
+      <c r="E8" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F8" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G8" s="3">
         <v>23803</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>46235</v>
       </c>
-      <c r="I8" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="I8" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH8" s="10"/>
+      <c r="AH8" s="8"/>
       <c r="AI8" s="9"/>
     </row>
-    <row r="9" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="4">
-        <v>35</v>
-      </c>
-      <c r="E9" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="C9" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="3">
+        <v>35</v>
+      </c>
+      <c r="E9" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F9" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G9" s="3">
         <v>23896</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>46235</v>
       </c>
-      <c r="I9" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="I9" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH9" s="10"/>
+      <c r="AH9" s="8"/>
       <c r="AI9" s="9"/>
     </row>
-    <row r="10" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="4">
-        <v>35</v>
-      </c>
-      <c r="E10" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="C10" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="3">
+        <v>35</v>
+      </c>
+      <c r="E10" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F10" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G10" s="3">
         <v>24307</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>46266</v>
       </c>
-      <c r="I10" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J10" s="4" t="s">
+      <c r="I10" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH10" s="10"/>
+      <c r="AH10" s="8"/>
       <c r="AI10" s="9"/>
     </row>
-    <row r="11" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="4">
-        <v>35</v>
-      </c>
-      <c r="E11" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="C11" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="3">
+        <v>35</v>
+      </c>
+      <c r="E11" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F11" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G11" s="3">
         <v>24412</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>46266</v>
       </c>
-      <c r="I11" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J11" s="4" t="s">
+      <c r="I11" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH11" s="10"/>
+      <c r="AH11" s="8"/>
       <c r="AI11" s="9"/>
     </row>
-    <row r="12" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="4">
-        <v>35</v>
-      </c>
-      <c r="E12" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="C12" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="3">
+        <v>35</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F12" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G12" s="3">
         <v>24334</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>46266</v>
       </c>
-      <c r="I12" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="8" t="s">
+      <c r="I12" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH12" s="10"/>
+      <c r="AH12" s="8"/>
       <c r="AI12" s="9"/>
     </row>
-    <row r="13" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="4">
-        <v>35</v>
-      </c>
-      <c r="E13" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F13" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="C13" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="3">
+        <v>35</v>
+      </c>
+      <c r="E13" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F13" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G13" s="3">
         <v>24484</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>46266</v>
       </c>
-      <c r="I13" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="8" t="s">
+      <c r="I13" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH13" s="10"/>
+      <c r="AH13" s="8"/>
       <c r="AI13" s="9"/>
     </row>
-    <row r="14" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="4">
-        <v>35</v>
-      </c>
-      <c r="E14" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="C14" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="3">
+        <v>35</v>
+      </c>
+      <c r="E14" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F14" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G14" s="3">
         <v>24488</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>46266</v>
       </c>
-      <c r="I14" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="8" t="s">
+      <c r="I14" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH14" s="10"/>
+      <c r="AH14" s="8"/>
       <c r="AI14" s="9"/>
     </row>
-    <row r="15" spans="1:35" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="4">
-        <v>35</v>
-      </c>
-      <c r="E15" s="6">
-        <v>46273</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46276</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="C15" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="3">
+        <v>35</v>
+      </c>
+      <c r="E15" s="5">
+        <v>46273</v>
+      </c>
+      <c r="F15" s="5">
+        <v>46276</v>
+      </c>
+      <c r="G15" s="3">
         <v>24507</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>46266</v>
       </c>
-      <c r="I15" s="6">
-        <v>46273</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="I15" s="5">
+        <v>46273</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AH15" s="10"/>
+      <c r="AH15" s="8"/>
       <c r="AI15" s="9"/>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{91B50299-36AF-40C0-B125-46DC9157643A}">

--- a/data/base/Backlog_35.xlsx
+++ b/data/base/Backlog_35.xlsx
@@ -620,31 +620,30 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1025,55 +1024,54 @@
   <dimension ref="A1:AT27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="40.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="34.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="255.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="33.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="28" style="2" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="31" style="2" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="59.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="5.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="49" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="23" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="28" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="31" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
@@ -1112,1045 +1110,1045 @@
       </c>
     </row>
     <row r="2" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="3">
-        <v>35</v>
-      </c>
-      <c r="E2" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F2" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="C2" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="2">
+        <v>35</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G2" s="2">
         <v>23459</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>46235</v>
       </c>
-      <c r="I2" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="I2" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="8"/>
-      <c r="O2" s="9"/>
-      <c r="AS2" s="8"/>
-      <c r="AT2" s="9"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="7"/>
+      <c r="O2" s="8"/>
+      <c r="AS2" s="7"/>
+      <c r="AT2" s="8"/>
     </row>
     <row r="3" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="3">
-        <v>35</v>
-      </c>
-      <c r="E3" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F3" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="C3" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="2">
+        <v>35</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G3" s="2">
         <v>23491</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>46235</v>
       </c>
-      <c r="I3" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="I3" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="8"/>
-      <c r="O3" s="9"/>
-      <c r="AS3" s="8"/>
-      <c r="AT3" s="9"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="7"/>
+      <c r="O3" s="8"/>
+      <c r="AS3" s="7"/>
+      <c r="AT3" s="8"/>
     </row>
     <row r="4" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="3">
-        <v>35</v>
-      </c>
-      <c r="E4" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F4" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="C4" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="2">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G4" s="2">
         <v>23747</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>46235</v>
       </c>
-      <c r="I4" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="I4" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="8"/>
-      <c r="O4" s="9"/>
-      <c r="AS4" s="8"/>
-      <c r="AT4" s="9"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="7"/>
+      <c r="O4" s="8"/>
+      <c r="AS4" s="7"/>
+      <c r="AT4" s="8"/>
     </row>
     <row r="5" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="3">
-        <v>35</v>
-      </c>
-      <c r="E5" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F5" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="C5" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="2">
+        <v>35</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G5" s="2">
         <v>23825</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>46235</v>
       </c>
-      <c r="I5" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="8"/>
-      <c r="O5" s="9"/>
-      <c r="AS5" s="8"/>
-      <c r="AT5" s="9"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="7"/>
+      <c r="O5" s="8"/>
+      <c r="AS5" s="7"/>
+      <c r="AT5" s="8"/>
     </row>
     <row r="6" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="3">
-        <v>35</v>
-      </c>
-      <c r="E6" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F6" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="C6" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="2">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G6" s="2">
         <v>23942</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>46235</v>
       </c>
-      <c r="I6" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="I6" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="8"/>
-      <c r="O6" s="9"/>
-      <c r="AS6" s="8"/>
-      <c r="AT6" s="9"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="7"/>
+      <c r="O6" s="8"/>
+      <c r="AS6" s="7"/>
+      <c r="AT6" s="8"/>
     </row>
     <row r="7" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="3">
-        <v>35</v>
-      </c>
-      <c r="E7" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F7" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="C7" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="2">
+        <v>35</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G7" s="2">
         <v>24002</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>46235</v>
       </c>
-      <c r="I7" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="I7" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="8"/>
-      <c r="O7" s="9"/>
-      <c r="AS7" s="8"/>
-      <c r="AT7" s="9"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="7"/>
+      <c r="O7" s="8"/>
+      <c r="AS7" s="7"/>
+      <c r="AT7" s="8"/>
     </row>
     <row r="8" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="3">
-        <v>35</v>
-      </c>
-      <c r="E8" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F8" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="C8" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="2">
+        <v>35</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G8" s="2">
         <v>24087</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>46235</v>
       </c>
-      <c r="I8" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="I8" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="8"/>
-      <c r="O8" s="9"/>
-      <c r="AS8" s="8"/>
-      <c r="AT8" s="9"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="7"/>
+      <c r="O8" s="8"/>
+      <c r="AS8" s="7"/>
+      <c r="AT8" s="8"/>
     </row>
     <row r="9" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="3">
-        <v>35</v>
-      </c>
-      <c r="E9" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F9" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="C9" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="2">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G9" s="2">
         <v>24100</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>46235</v>
       </c>
-      <c r="I9" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="7" t="s">
+      <c r="I9" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="8"/>
-      <c r="AS9" s="8"/>
-      <c r="AT9" s="9"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="7"/>
+      <c r="AS9" s="7"/>
+      <c r="AT9" s="8"/>
     </row>
     <row r="10" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="3">
-        <v>35</v>
-      </c>
-      <c r="E10" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F10" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="C10" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="2">
+        <v>35</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G10" s="2">
         <v>24204</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>46266</v>
       </c>
-      <c r="I10" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="7" t="s">
+      <c r="I10" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="9"/>
-      <c r="M10" s="8"/>
-      <c r="O10" s="9"/>
-      <c r="AS10" s="8"/>
-      <c r="AT10" s="9"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="7"/>
+      <c r="O10" s="8"/>
+      <c r="AS10" s="7"/>
+      <c r="AT10" s="8"/>
     </row>
     <row r="11" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="3">
-        <v>35</v>
-      </c>
-      <c r="E11" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F11" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="C11" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="2">
+        <v>35</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G11" s="2">
         <v>24215</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>46266</v>
       </c>
-      <c r="I11" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="7" t="s">
+      <c r="I11" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="8"/>
-      <c r="O11" s="9"/>
-      <c r="AS11" s="8"/>
-      <c r="AT11" s="9"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="7"/>
+      <c r="O11" s="8"/>
+      <c r="AS11" s="7"/>
+      <c r="AT11" s="8"/>
     </row>
     <row r="12" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="3">
-        <v>35</v>
-      </c>
-      <c r="E12" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F12" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="C12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="2">
+        <v>35</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G12" s="2">
         <v>24222</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>46266</v>
       </c>
-      <c r="I12" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="I12" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="8"/>
-      <c r="O12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AS12" s="8"/>
-      <c r="AT12" s="9"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="7"/>
+      <c r="O12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AS12" s="7"/>
+      <c r="AT12" s="8"/>
     </row>
     <row r="13" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="3">
-        <v>35</v>
-      </c>
-      <c r="E13" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F13" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="C13" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="2">
+        <v>35</v>
+      </c>
+      <c r="E13" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G13" s="2">
         <v>24224</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>46266</v>
       </c>
-      <c r="I13" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="7" t="s">
+      <c r="I13" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="8"/>
-      <c r="O13" s="9"/>
-      <c r="AS13" s="8"/>
-      <c r="AT13" s="9"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="7"/>
+      <c r="O13" s="8"/>
+      <c r="AS13" s="7"/>
+      <c r="AT13" s="8"/>
     </row>
     <row r="14" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="3">
-        <v>35</v>
-      </c>
-      <c r="E14" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F14" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="C14" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="2">
+        <v>35</v>
+      </c>
+      <c r="E14" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G14" s="2">
         <v>24226</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>46266</v>
       </c>
-      <c r="I14" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="7" t="s">
+      <c r="I14" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="8"/>
-      <c r="AS14" s="8"/>
-      <c r="AT14" s="9"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="7"/>
+      <c r="AS14" s="7"/>
+      <c r="AT14" s="8"/>
     </row>
     <row r="15" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="3">
-        <v>35</v>
-      </c>
-      <c r="E15" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F15" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="C15" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="2">
+        <v>35</v>
+      </c>
+      <c r="E15" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G15" s="2">
         <v>24231</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>46266</v>
       </c>
-      <c r="I15" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="7" t="s">
+      <c r="I15" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="8"/>
-      <c r="AS15" s="8"/>
-      <c r="AT15" s="9"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="7"/>
+      <c r="AS15" s="7"/>
+      <c r="AT15" s="8"/>
     </row>
     <row r="16" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="3">
-        <v>35</v>
-      </c>
-      <c r="E16" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F16" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="C16" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="2">
+        <v>35</v>
+      </c>
+      <c r="E16" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G16" s="2">
         <v>24245</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>46266</v>
       </c>
-      <c r="I16" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="7" t="s">
+      <c r="I16" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="8"/>
-      <c r="O16" s="9"/>
-      <c r="AS16" s="8"/>
-      <c r="AT16" s="9"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="7"/>
+      <c r="O16" s="8"/>
+      <c r="AS16" s="7"/>
+      <c r="AT16" s="8"/>
     </row>
     <row r="17" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="3">
-        <v>35</v>
-      </c>
-      <c r="E17" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F17" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="C17" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="2">
+        <v>35</v>
+      </c>
+      <c r="E17" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G17" s="2">
         <v>24248</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>46266</v>
       </c>
-      <c r="I17" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="7" t="s">
+      <c r="I17" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="8"/>
-      <c r="O17" s="9"/>
-      <c r="AS17" s="8"/>
-      <c r="AT17" s="9"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="7"/>
+      <c r="O17" s="8"/>
+      <c r="AS17" s="7"/>
+      <c r="AT17" s="8"/>
     </row>
     <row r="18" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="3">
-        <v>35</v>
-      </c>
-      <c r="E18" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F18" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="C18" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="2">
+        <v>35</v>
+      </c>
+      <c r="E18" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F18" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G18" s="2">
         <v>24287</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>46266</v>
       </c>
-      <c r="I18" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="7" t="s">
+      <c r="I18" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="8"/>
-      <c r="O18" s="9"/>
-      <c r="AS18" s="8"/>
-      <c r="AT18" s="9"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="7"/>
+      <c r="O18" s="8"/>
+      <c r="AS18" s="7"/>
+      <c r="AT18" s="8"/>
     </row>
     <row r="19" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="3">
-        <v>35</v>
-      </c>
-      <c r="E19" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F19" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G19" s="3">
+      <c r="C19" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="2">
+        <v>35</v>
+      </c>
+      <c r="E19" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G19" s="2">
         <v>24342</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>46266</v>
       </c>
-      <c r="I19" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="7" t="s">
+      <c r="I19" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="8"/>
-      <c r="O19" s="9"/>
-      <c r="AS19" s="8"/>
-      <c r="AT19" s="9"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="7"/>
+      <c r="O19" s="8"/>
+      <c r="AS19" s="7"/>
+      <c r="AT19" s="8"/>
     </row>
     <row r="20" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="3">
-        <v>35</v>
-      </c>
-      <c r="E20" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F20" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="C20" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="2">
+        <v>35</v>
+      </c>
+      <c r="E20" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G20" s="2">
         <v>24343</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>46266</v>
       </c>
-      <c r="I20" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="7" t="s">
+      <c r="I20" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="8"/>
-      <c r="O20" s="9"/>
-      <c r="AS20" s="8"/>
-      <c r="AT20" s="9"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="7"/>
+      <c r="O20" s="8"/>
+      <c r="AS20" s="7"/>
+      <c r="AT20" s="8"/>
     </row>
     <row r="21" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="3">
-        <v>35</v>
-      </c>
-      <c r="E21" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F21" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="C21" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="2">
+        <v>35</v>
+      </c>
+      <c r="E21" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G21" s="2">
         <v>24344</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>46266</v>
       </c>
-      <c r="I21" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="7" t="s">
+      <c r="I21" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="9"/>
-      <c r="M21" s="8"/>
-      <c r="O21" s="9"/>
-      <c r="AS21" s="8"/>
-      <c r="AT21" s="9"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="7"/>
+      <c r="O21" s="8"/>
+      <c r="AS21" s="7"/>
+      <c r="AT21" s="8"/>
     </row>
     <row r="22" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="3">
-        <v>35</v>
-      </c>
-      <c r="E22" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F22" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="C22" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="2">
+        <v>35</v>
+      </c>
+      <c r="E22" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F22" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G22" s="2">
         <v>24366</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>46266</v>
       </c>
-      <c r="I22" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="7" t="s">
+      <c r="I22" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="8"/>
-      <c r="O22" s="9"/>
-      <c r="AS22" s="8"/>
-      <c r="AT22" s="9"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="7"/>
+      <c r="O22" s="8"/>
+      <c r="AS22" s="7"/>
+      <c r="AT22" s="8"/>
     </row>
     <row r="23" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="3">
-        <v>35</v>
-      </c>
-      <c r="E23" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F23" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="C23" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="2">
+        <v>35</v>
+      </c>
+      <c r="E23" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F23" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G23" s="2">
         <v>24404</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>46266</v>
       </c>
-      <c r="I23" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J23" s="4" t="s">
+      <c r="I23" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="8"/>
-      <c r="O23" s="9"/>
-      <c r="AS23" s="8"/>
-      <c r="AT23" s="9"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="7"/>
+      <c r="O23" s="8"/>
+      <c r="AS23" s="7"/>
+      <c r="AT23" s="8"/>
     </row>
     <row r="24" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="3">
-        <v>35</v>
-      </c>
-      <c r="E24" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F24" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="C24" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="2">
+        <v>35</v>
+      </c>
+      <c r="E24" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F24" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G24" s="2">
         <v>24416</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>46266</v>
       </c>
-      <c r="I24" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J24" s="4" t="s">
+      <c r="I24" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="9"/>
-      <c r="M24" s="8"/>
-      <c r="O24" s="9"/>
-      <c r="AS24" s="8"/>
-      <c r="AT24" s="9"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="7"/>
+      <c r="O24" s="8"/>
+      <c r="AS24" s="7"/>
+      <c r="AT24" s="8"/>
     </row>
     <row r="25" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="3">
-        <v>35</v>
-      </c>
-      <c r="E25" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F25" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G25" s="3">
+      <c r="C25" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="2">
+        <v>35</v>
+      </c>
+      <c r="E25" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G25" s="2">
         <v>24424</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>46266</v>
       </c>
-      <c r="I25" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="7" t="s">
+      <c r="I25" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="9"/>
-      <c r="M25" s="8"/>
-      <c r="O25" s="9"/>
-      <c r="AS25" s="8"/>
-      <c r="AT25" s="9"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="7"/>
+      <c r="O25" s="8"/>
+      <c r="AS25" s="7"/>
+      <c r="AT25" s="8"/>
     </row>
     <row r="26" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="3">
-        <v>35</v>
-      </c>
-      <c r="E26" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F26" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="C26" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="2">
+        <v>35</v>
+      </c>
+      <c r="E26" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G26" s="2">
         <v>24444</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="5">
         <v>46266</v>
       </c>
-      <c r="I26" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J26" s="4" t="s">
+      <c r="I26" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="K26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="9"/>
-      <c r="M26" s="8"/>
-      <c r="O26" s="9"/>
-      <c r="AS26" s="8"/>
-      <c r="AT26" s="9"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="7"/>
+      <c r="O26" s="8"/>
+      <c r="AS26" s="7"/>
+      <c r="AT26" s="8"/>
     </row>
     <row r="27" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="3">
-        <v>35</v>
-      </c>
-      <c r="E27" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F27" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="C27" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="2">
+        <v>35</v>
+      </c>
+      <c r="E27" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F27" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G27" s="2">
         <v>24451</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>46266</v>
       </c>
-      <c r="I27" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K27" s="7" t="s">
+      <c r="I27" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="8"/>
-      <c r="O27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AS27" s="8"/>
-      <c r="AT27" s="9"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="7"/>
+      <c r="O27" s="8"/>
+      <c r="Y27" s="8"/>
+      <c r="Z27" s="8"/>
+      <c r="AS27" s="7"/>
+      <c r="AT27" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{349D8DFF-FFE7-45CA-B67A-40C93DB9EFC7}"/>
@@ -2163,43 +2161,42 @@
   <dimension ref="A1:AI18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="33.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="59.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
@@ -2238,536 +2235,536 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="3">
-        <v>35</v>
-      </c>
-      <c r="E2" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F2" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="C2" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="2">
+        <v>35</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G2" s="2">
         <v>24123</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>46235</v>
       </c>
-      <c r="I2" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH2" s="8"/>
-      <c r="AI2" s="9"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="8"/>
     </row>
     <row r="3" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="3">
-        <v>35</v>
-      </c>
-      <c r="E3" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F3" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="C3" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="2">
+        <v>35</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G3" s="2">
         <v>24062</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>46235</v>
       </c>
-      <c r="I3" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="I3" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="9"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="8"/>
     </row>
     <row r="4" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="3">
-        <v>35</v>
-      </c>
-      <c r="E4" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F4" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="C4" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="2">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G4" s="2">
         <v>24182</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>46266</v>
       </c>
-      <c r="I4" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="I4" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH4" s="8"/>
-      <c r="AI4" s="9"/>
+      <c r="AH4" s="7"/>
+      <c r="AI4" s="8"/>
     </row>
     <row r="5" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="3">
-        <v>35</v>
-      </c>
-      <c r="E5" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F5" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="C5" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="2">
+        <v>35</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G5" s="2">
         <v>24284</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>46266</v>
       </c>
-      <c r="I5" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="I5" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH5" s="8"/>
-      <c r="AI5" s="9"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="8"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="3">
-        <v>35</v>
-      </c>
-      <c r="E6" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F6" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="C6" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="2">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G6" s="2">
         <v>22908</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>46235</v>
       </c>
-      <c r="I6" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="I6" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="AH6" s="8"/>
-      <c r="AI6" s="9"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="8"/>
     </row>
     <row r="7" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="3">
-        <v>35</v>
-      </c>
-      <c r="E7" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F7" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="C7" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="2">
+        <v>35</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G7" s="2">
         <v>23490</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>46235</v>
       </c>
-      <c r="I7" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="I7" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH7" s="8"/>
-      <c r="AI7" s="9"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="8"/>
     </row>
     <row r="8" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="3">
-        <v>35</v>
-      </c>
-      <c r="E8" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F8" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="C8" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="2">
+        <v>35</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G8" s="2">
         <v>23803</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>46235</v>
       </c>
-      <c r="I8" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="I8" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH8" s="8"/>
-      <c r="AI8" s="9"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="8"/>
     </row>
     <row r="9" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="3">
-        <v>35</v>
-      </c>
-      <c r="E9" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F9" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="C9" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="2">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G9" s="2">
         <v>23896</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>46235</v>
       </c>
-      <c r="I9" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="7" t="s">
+      <c r="I9" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH9" s="8"/>
-      <c r="AI9" s="9"/>
+      <c r="AH9" s="7"/>
+      <c r="AI9" s="8"/>
     </row>
     <row r="10" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="3">
-        <v>35</v>
-      </c>
-      <c r="E10" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F10" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="C10" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="2">
+        <v>35</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G10" s="2">
         <v>24307</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>46266</v>
       </c>
-      <c r="I10" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="I10" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH10" s="8"/>
-      <c r="AI10" s="9"/>
+      <c r="AH10" s="7"/>
+      <c r="AI10" s="8"/>
     </row>
     <row r="11" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="3">
-        <v>35</v>
-      </c>
-      <c r="E11" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F11" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="C11" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="2">
+        <v>35</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G11" s="2">
         <v>24412</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>46266</v>
       </c>
-      <c r="I11" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="I11" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH11" s="8"/>
-      <c r="AI11" s="9"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="8"/>
     </row>
     <row r="12" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="3">
-        <v>35</v>
-      </c>
-      <c r="E12" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F12" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="C12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="2">
+        <v>35</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G12" s="2">
         <v>24334</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>46266</v>
       </c>
-      <c r="I12" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="I12" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH12" s="8"/>
-      <c r="AI12" s="9"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="8"/>
     </row>
     <row r="13" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="3">
-        <v>35</v>
-      </c>
-      <c r="E13" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F13" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="C13" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="2">
+        <v>35</v>
+      </c>
+      <c r="E13" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G13" s="2">
         <v>24484</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>46266</v>
       </c>
-      <c r="I13" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="7" t="s">
+      <c r="I13" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH13" s="8"/>
-      <c r="AI13" s="9"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="8"/>
     </row>
     <row r="14" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="3">
-        <v>35</v>
-      </c>
-      <c r="E14" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F14" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="C14" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="2">
+        <v>35</v>
+      </c>
+      <c r="E14" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G14" s="2">
         <v>24488</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>46266</v>
       </c>
-      <c r="I14" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="7" t="s">
+      <c r="I14" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="9"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="8"/>
     </row>
     <row r="15" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="3">
-        <v>35</v>
-      </c>
-      <c r="E15" s="5">
-        <v>46273</v>
-      </c>
-      <c r="F15" s="5">
-        <v>46276</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="C15" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="2">
+        <v>35</v>
+      </c>
+      <c r="E15" s="4">
+        <v>46273</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46276</v>
+      </c>
+      <c r="G15" s="2">
         <v>24507</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>46266</v>
       </c>
-      <c r="I15" s="5">
-        <v>46273</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="7" t="s">
+      <c r="I15" s="4">
+        <v>46273</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AH15" s="8"/>
-      <c r="AI15" s="9"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="8"/>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{91B50299-36AF-40C0-B125-46DC9157643A}">
